--- a/artfynd/A 55394-2021 artfynd.xlsx
+++ b/artfynd/A 55394-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55394-2021 artfynd.xlsx
+++ b/artfynd/A 55394-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99114492</v>
+        <v>99114466</v>
       </c>
       <c r="B2" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>374525.2954932431</v>
+        <v>374638</v>
       </c>
       <c r="R2" t="n">
-        <v>6921042.435575352</v>
+        <v>6921010</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99114493</v>
+        <v>99114469</v>
       </c>
       <c r="B3" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>374556.1122497916</v>
+        <v>374485</v>
       </c>
       <c r="R3" t="n">
-        <v>6921070.979198721</v>
+        <v>6920955</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99114466</v>
+        <v>99114470</v>
       </c>
       <c r="B4" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>374637.4753744087</v>
+        <v>374523</v>
       </c>
       <c r="R4" t="n">
-        <v>6921009.913016616</v>
+        <v>6920985</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99114499</v>
+        <v>99114478</v>
       </c>
       <c r="B5" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>374570.8991910609</v>
+        <v>374626</v>
       </c>
       <c r="R5" t="n">
-        <v>6921006.84388405</v>
+        <v>6920984</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1034,9 @@
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99114478</v>
+        <v>99114485</v>
       </c>
       <c r="B6" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>374625.8091628164</v>
+        <v>374485</v>
       </c>
       <c r="R6" t="n">
-        <v>6920983.8977627</v>
+        <v>6920955</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1131,9 @@
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99114470</v>
+        <v>99114492</v>
       </c>
       <c r="B7" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>967</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>374523.1536597601</v>
+        <v>374526</v>
       </c>
       <c r="R7" t="n">
-        <v>6920985.432910466</v>
+        <v>6921043</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1308,19 +1228,9 @@
           <t>2022-03-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-03-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,6 +1254,200 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>99114493</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Övre Mysklan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>374556</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6921071</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-03-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-03-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>99114499</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Övre Mysklan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>374571</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6921007</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-03-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-03-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55394-2021 artfynd.xlsx
+++ b/artfynd/A 55394-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99114466</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99114469</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99114470</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99114478</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99114485</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99114492</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99114493</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,8 +1488,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99114499</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>